--- a/stories/arbres/TREE-COL-021.xlsx
+++ b/stories/arbres/TREE-COL-021.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Jules est avec papa, sur le chemin de l'école. Jules a envie de jouer. papa est là, tout près. On va apprendre : Tour de parole. Voici le geste : lever la main ; attendre. Jules écoute papa. Jules entend les mots : attendre, puis parler.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jules va vers la cuisine. Une feuille tombe. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Jules se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On dit merci. papa dit : je suis là. On reste ensemble.</t>
+          <t>Jules va vers la cuisine. Une feuille tombe. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Jules se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On dit merci. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Jules va vers la cuisine. Une feuille tombe. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Jules se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On dit merci.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1858,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Tour de parole.</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2031,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : lever la main ; attendre. Jules respire. Jules retient : attendre, puis parler. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2222,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2389,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2580,11 @@
         <v>12</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2747,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le matin. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la cuisine, les cubes et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2914,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3081,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint après la sieste. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3248,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3337,6 +3415,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le soir. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, les cubes et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3582,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,6 +3749,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On montre du doigt, sans courir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3940,11 @@
         <v>12</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4009,6 +4107,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le matin. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la cuisine, le livre et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4274,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4441,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint après la sieste. La couverture est douce. On souffle doucement. Cette fin-là est celle de la cuisine, le livre et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4608,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4657,6 +4775,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le soir. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, le livre et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4942,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4981,6 +5109,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On rit un peu. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5300,11 @@
         <v>12</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5329,6 +5467,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le matin. La couverture est douce. On dit merci. Cette fin-là est celle de la cuisine, la dînette et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5634,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5653,6 +5801,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint après la sieste. On entend un oiseau. On souffle doucement. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5968,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5977,6 +6135,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le soir. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, la dînette et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6302,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6163,7 +6331,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Jules va vers le jardin. L'eau coule, tout petit bruit. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Jules se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On souffle doucement. papa dit : je suis là. On reste ensemble.</t>
+          <t>Jules va vers le jardin. L'eau coule, tout petit bruit. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Jules se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On souffle doucement. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6301,6 +6469,12 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Jules va vers le jardin. L'eau coule, tout petit bruit. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Jules se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On souffle doucement.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6477,6 +6651,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Tour de parole.</t>
         </is>
       </c>
     </row>
@@ -6645,6 +6824,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : lever la main ; attendre. Jules respire. Jules retient : attendre, puis parler. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6831,6 +7015,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6993,6 +7182,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi les cubes. Un chat miaule une fois. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7179,6 +7373,11 @@
         <v>12</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7341,6 +7540,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le matin. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7503,6 +7707,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7665,6 +7874,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint après la sieste. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, les cubes et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7827,6 +8041,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7989,6 +8208,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le soir. On entend un oiseau. On attend son tour. Cette fin-là est celle de le jardin, les cubes et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8151,6 +8375,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8313,6 +8542,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le livre. Les chaussures font toc toc. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On montre du doigt, sans courir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8499,6 +8733,11 @@
         <v>12</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8661,6 +8900,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le matin. La couverture est douce. On souffle doucement. Cette fin-là est celle de le jardin, le livre et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8823,6 +9067,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8985,6 +9234,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint après la sieste. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, le livre et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9147,6 +9401,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9309,6 +9568,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le soir. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de le jardin, le livre et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9471,6 +9735,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9633,6 +9902,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi la dînette. La couverture est douce. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On rit un peu. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9819,6 +10093,11 @@
         <v>12</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9981,6 +10260,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le matin. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10143,6 +10427,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10305,6 +10594,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint après la sieste. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, la dînette et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10467,6 +10761,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10629,6 +10928,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le soir. Le vent est doux. On attend son tour. Cette fin-là est celle de le jardin, la dînette et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10791,6 +11095,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10815,7 +11124,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Jules va vers la chambre. Un vélo passe au loin. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Jules se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On écoute jusqu'au bout. papa dit : je suis là. On reste ensemble.</t>
+          <t>Jules va vers la chambre. Un vélo passe au loin. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Jules se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On écoute jusqu'au bout. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10953,6 +11262,12 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Jules va vers la chambre. Un vélo passe au loin. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Jules se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On écoute jusqu'au bout.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11129,6 +11444,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Tour de parole.</t>
         </is>
       </c>
     </row>
@@ -11297,6 +11617,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : lever la main ; attendre. Jules respire. Jules retient : attendre, puis parler. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11483,6 +11808,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11645,6 +11975,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11831,6 +12166,11 @@
         <v>12</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11993,6 +12333,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le matin. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12155,6 +12500,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12317,6 +12667,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint après la sieste. On entend un oiseau. On attend son tour. Cette fin-là est celle de la chambre, les cubes et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12479,6 +12834,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12641,6 +13001,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le soir. Ça sent le pain chaud. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, les cubes et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12803,6 +13168,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12965,6 +13335,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On montre du doigt, sans courir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13151,6 +13526,11 @@
         <v>12</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13313,6 +13693,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le matin. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13475,6 +13860,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13637,6 +14027,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint après la sieste. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de la chambre, le livre et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13799,6 +14194,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13961,6 +14361,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le soir. Le vent est doux. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, le livre et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14123,6 +14528,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14285,6 +14695,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On rit un peu. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14471,6 +14886,11 @@
         <v>12</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14633,6 +15053,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le matin. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14795,6 +15220,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14957,6 +15387,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint après la sieste. Le vent est doux. On attend son tour. Cette fin-là est celle de la chambre, la dînette et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15119,6 +15554,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15281,6 +15721,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le soir. Le sol est un peu froid. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, la dînette et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15443,6 +15888,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15461,7 +15911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15478,6 +15928,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-021.xlsx
+++ b/stories/arbres/TREE-COL-021.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Jules est avec papa, sur le chemin de l'école. Jules a envie de jouer. papa est là, tout près. On va apprendre : Tour de parole. Voici le geste : lever la main ; attendre. Jules écoute papa. Jules entend les mots : attendre, puis parler.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1865,6 +1873,7 @@
           <t>narrateur|Que fait-on ? Tour de parole.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2036,6 +2045,7 @@
           <t>narrateur|Oui. Voici le geste : lever la main ; attendre. Jules respire. Jules retient : attendre, puis parler. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2227,6 +2237,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2394,6 +2405,7 @@
           <t>narrateur|Jules a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2585,6 +2597,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2752,6 +2765,7 @@
           <t>narrateur|Jules rejoint le matin. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la cuisine, les cubes et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2919,6 +2933,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3086,6 +3101,7 @@
           <t>narrateur|Jules rejoint après la sieste. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3253,6 +3269,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3420,6 +3437,7 @@
           <t>narrateur|Jules rejoint le soir. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, les cubes et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3587,6 +3605,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3754,6 +3773,7 @@
           <t>narrateur|Jules a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On montre du doigt, sans courir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3945,6 +3965,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4112,6 +4133,7 @@
           <t>narrateur|Jules rejoint le matin. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la cuisine, le livre et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4279,6 +4301,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4446,6 +4469,7 @@
           <t>narrateur|Jules rejoint après la sieste. La couverture est douce. On souffle doucement. Cette fin-là est celle de la cuisine, le livre et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4613,6 +4637,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4780,6 +4805,7 @@
           <t>narrateur|Jules rejoint le soir. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, le livre et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4947,6 +4973,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5114,6 +5141,7 @@
           <t>narrateur|Jules a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On rit un peu. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5305,6 +5333,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5472,6 +5501,7 @@
           <t>narrateur|Jules rejoint le matin. La couverture est douce. On dit merci. Cette fin-là est celle de la cuisine, la dînette et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5639,6 +5669,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5806,6 +5837,7 @@
           <t>narrateur|Jules rejoint après la sieste. On entend un oiseau. On souffle doucement. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5973,6 +6005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6140,6 +6173,7 @@
           <t>narrateur|Jules rejoint le soir. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, la dînette et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6307,6 +6341,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6475,6 +6510,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6658,6 +6694,7 @@
           <t>narrateur|Que fait-on ? Tour de parole.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6829,6 +6866,7 @@
           <t>narrateur|Oui. Voici le geste : lever la main ; attendre. Jules respire. Jules retient : attendre, puis parler. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7020,6 +7058,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7187,6 +7226,7 @@
           <t>narrateur|Jules a choisi les cubes. Un chat miaule une fois. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7378,6 +7418,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7545,6 +7586,7 @@
           <t>narrateur|Jules rejoint le matin. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7712,6 +7754,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7879,6 +7922,7 @@
           <t>narrateur|Jules rejoint après la sieste. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, les cubes et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8046,6 +8090,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8213,6 +8258,7 @@
           <t>narrateur|Jules rejoint le soir. On entend un oiseau. On attend son tour. Cette fin-là est celle de le jardin, les cubes et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8380,6 +8426,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8547,6 +8594,7 @@
           <t>narrateur|Jules a choisi le livre. Les chaussures font toc toc. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On montre du doigt, sans courir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8738,6 +8786,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8905,6 +8954,7 @@
           <t>narrateur|Jules rejoint le matin. La couverture est douce. On souffle doucement. Cette fin-là est celle de le jardin, le livre et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9072,6 +9122,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9239,6 +9290,7 @@
           <t>narrateur|Jules rejoint après la sieste. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, le livre et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9406,6 +9458,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9573,6 +9626,7 @@
           <t>narrateur|Jules rejoint le soir. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de le jardin, le livre et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9740,6 +9794,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9907,6 +9962,7 @@
           <t>narrateur|Jules a choisi la dînette. La couverture est douce. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On rit un peu. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10098,6 +10154,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10265,6 +10322,7 @@
           <t>narrateur|Jules rejoint le matin. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10432,6 +10490,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10599,6 +10658,7 @@
           <t>narrateur|Jules rejoint après la sieste. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, la dînette et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10766,6 +10826,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10933,6 +10994,7 @@
           <t>narrateur|Jules rejoint le soir. Le vent est doux. On attend son tour. Cette fin-là est celle de le jardin, la dînette et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11100,6 +11162,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11268,6 +11331,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11451,6 +11515,7 @@
           <t>narrateur|Que fait-on ? Tour de parole.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11622,6 +11687,7 @@
           <t>narrateur|Oui. Voici le geste : lever la main ; attendre. Jules respire. Jules retient : attendre, puis parler. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11813,6 +11879,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11980,6 +12047,7 @@
           <t>narrateur|Jules a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12171,6 +12239,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12338,6 +12407,7 @@
           <t>narrateur|Jules rejoint le matin. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12505,6 +12575,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12672,6 +12743,7 @@
           <t>narrateur|Jules rejoint après la sieste. On entend un oiseau. On attend son tour. Cette fin-là est celle de la chambre, les cubes et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12839,6 +12911,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13006,6 +13079,7 @@
           <t>narrateur|Jules rejoint le soir. Ça sent le pain chaud. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, les cubes et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13173,6 +13247,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13340,6 +13415,7 @@
           <t>narrateur|Jules a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On montre du doigt, sans courir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13531,6 +13607,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13698,6 +13775,7 @@
           <t>narrateur|Jules rejoint le matin. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13865,6 +13943,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14032,6 +14111,7 @@
           <t>narrateur|Jules rejoint après la sieste. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de la chambre, le livre et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14199,6 +14279,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14366,6 +14447,7 @@
           <t>narrateur|Jules rejoint le soir. Le vent est doux. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, le livre et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14533,6 +14615,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14700,6 +14783,7 @@
           <t>narrateur|Jules a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On rit un peu. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14891,6 +14975,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15058,6 +15143,7 @@
           <t>narrateur|Jules rejoint le matin. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15225,6 +15311,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15392,6 +15479,7 @@
           <t>narrateur|Jules rejoint après la sieste. Le vent est doux. On attend son tour. Cette fin-là est celle de la chambre, la dînette et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15559,6 +15647,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15726,6 +15815,7 @@
           <t>narrateur|Jules rejoint le soir. Le sol est un peu froid. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, la dînette et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15893,6 +15983,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15911,7 +16002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15935,6 +16026,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15949,7 +16054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16136,6 +16241,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-COL-021.xlsx
+++ b/stories/arbres/TREE-COL-021.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tour de parole — sur le chemin de l'école</t>
+          <t>La flaque et le ciré de Victorino</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une flaque tient le ciel, sous la boîte. Victorino rentre. Il lève la main, il attend, puis il parle, avec papa et maman.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aujourd'hui, Jules est avec papa, sur le chemin de l'école. Jules a envie de jouer. papa est là, tout près. On va apprendre : Tour de parole. Voici le geste : lever la main ; attendre. Jules écoute papa. Jules entend les mots : attendre, puis parler.</t>
+          <t>Une flaque tient le ciel, sous la boîte. Le ciré jaune pend au crochet. Le capuchon goutte, tout lourd. Un gant de laine chauffe sur le radiateur. Ça sent le cacao, tout chaud. La vapeur embue la vitre de la porte. Le cartable attend sur la première marche. Dehors, le chemin de l'école brille. Une feuille jaune colle au portail. Ton gant est tout chaud, Victorino. Tu as vu la flaque ? Elle tient le ciel. Oui. Elle est ronde, comme un miroir. Papa pose deux tasses près de la vitre. Le cacao fait un petit nuage. En ce moment, Victorino est dans l'entrée. Il a une chose à dire. J'ai une chose. On lève la main. On attend. Puis on parle. Tu peux lever la main. Papa parle déjà, tout doucement. Victorino lève la main. Il attend. Bravo. C'est ton tour. Le chemin brille, dehors. Tu as attendu. Puis tu as parlé. Une goutte tombe encore du capuchon. On reste un moment, à la maison.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,10 +1337,46 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aujourd'hui, Jules est avec papa, sur le chemin de l'école. Jules a envie de jouer. papa est là, tout près. On va apprendre : Tour de parole. Voici le geste : lever la main ; attendre. Jules écoute papa. Jules entend les mots : attendre, puis parler.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Une flaque tient le ciel, sous la boîte.
+narrateur|Le ciré jaune pend au crochet.
+narrateur|Le capuchon goutte, tout lourd.
+narrateur|Un gant de laine chauffe sur le radiateur.
+narrateur|Ça sent le cacao, tout chaud.
+narrateur|La vapeur embue la vitre de la porte.
+narrateur|Le cartable attend sur la première marche.
+narrateur|Dehors, le chemin de l'école brille.
+narrateur|Une feuille jaune colle au portail.
+papa|Ton gant est tout chaud, Victorino.
+maman|Tu as vu la flaque ?
+enfant-m|Elle tient le ciel.
+maman|Oui.
+maman|Elle est ronde, comme un miroir.
+narrateur|Papa pose deux tasses près de la vitre.
+narrateur|Le cacao fait un petit nuage.
+narrateur|En ce moment, Victorino est dans l'entrée.
+narrateur|Il a une chose à dire.
+enfant-m|J'ai une chose.
+papa|On lève la main.
+papa|On attend.
+papa|Puis on parle.
+maman|Tu peux lever la main.
+narrateur|Papa parle déjà, tout doucement.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+maman|Bravo.
+maman|C'est ton tour.
+enfant-m|Le chemin brille, dehors.
+papa|Tu as attendu.
+papa|Puis tu as parlé.
+narrateur|Une goutte tombe encore du capuchon.
+maman|On reste un moment, à la maison.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>goutte,cacao</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1353,7 +1401,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>Où va Victorino, maintenant ? La cuisine, le jardin, ou la chambre ? On s'écoute. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1517,7 +1565,11 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>narrateur|Où va Victorino, maintenant ?
+papa|La cuisine, le jardin, ou la chambre ?
+maman|On s'écoute.
+maman|On attend.
+maman|Puis on parle.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1545,7 +1597,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jules va vers la cuisine. Une feuille tombe. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Jules se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On dit merci. Je suis là. On reste ensemble.</t>
+          <t>Victorino pousse la porte de la cuisine. Le cacao fume encore, dans les tasses. Une cuillère en bois est un peu collante. Ça sent le pain grillé, tout doux. Moi, je raconte le cacao. Papa parle, près des tasses. Victorino a une chose à dire. Il lève la main. Il attend. La flaque tient le ciel. Oui. C'est ton tour. Tu as attendu. On lève la main. On attend. Puis on parle. Une goutte de cacao tombe dans la tasse. Le bois de la table est tiède.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1685,11 +1737,31 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Jules va vers la cuisine. Une feuille tombe. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Jules se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On dit merci.
-papa|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Victorino pousse la porte de la cuisine.
+narrateur|Le cacao fume encore, dans les tasses.
+narrateur|Une cuillère en bois est un peu collante.
+narrateur|Ça sent le pain grillé, tout doux.
+papa|Moi, je raconte le cacao.
+narrateur|Papa parle, près des tasses.
+narrateur|Victorino a une chose à dire.
+narrateur|Il lève la main.
+narrateur|Il attend.
+enfant-m|La flaque tient le ciel.
+maman|Oui.
+maman|C'est ton tour.
+maman|Tu as attendu.
+papa|On lève la main.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Une goutte de cacao tombe dans la tasse.
+narrateur|Le bois de la table est tiède.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>cacao,pain</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1714,7 +1786,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Tour de parole.</t>
+          <t>Victorino veut parler, près des tasses. Il fait quoi d'abord ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1870,7 +1942,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Tour de parole.</t>
+          <t>narrateur|Victorino veut parler, près des tasses.
+papa|Il fait quoi d'abord ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1898,7 +1971,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : lever la main ; attendre. Jules respire. Jules retient : attendre, puis parler. On continue, avec papa.</t>
+          <t>Oui. On lève la main. On attend. Puis on parle. Victorino souffle un peu. Sa main redescend, tout doux. J'ai attendu. Bravo. C'est du bon travail. Tu as fini de souffler ? Oui, maman.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2042,7 +2115,17 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : lever la main ; attendre. Jules respire. Jules retient : attendre, puis parler. On continue, avec papa.</t>
+          <t>papa|Oui.
+papa|On lève la main.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Victorino souffle un peu.
+narrateur|Sa main redescend, tout doux.
+enfant-m|J'ai attendu.
+maman|Bravo.
+maman|C'est du bon travail.
+maman|Tu as fini de souffler ?
+enfant-m|Oui, maman.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2070,7 +2153,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Trois jeux attendent, tout proches. Les cubes, le livre, ou la dînette ? On joue. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2234,7 +2317,11 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Trois jeux attendent, tout proches.
+maman|Les cubes, le livre, ou la dînette ?
+papa|On joue.
+papa|On attend.
+papa|Puis on parle.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2262,7 +2349,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On attend son tour. maman n'est pas loin.</t>
+          <t>Victorino prend les cubes en bois. Un cube rouge fait clic. Un cube jaune sent le pin. Moi, je raconte la tour. Papa parle. Victorino lève la main. Il attend. C'est ton tour. Une maison pour le ciel. Oui. Merci d'avoir attendu. On attend. Puis on parle. Victorino pose un cube, tout droit. Un cube attrape un reflet de cacao. On est encore dans la cuisine. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2402,10 +2489,31 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On attend son tour. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+          <t>narrateur|Victorino prend les cubes en bois.
+narrateur|Un cube rouge fait clic.
+narrateur|Un cube jaune sent le pin.
+papa|Moi, je raconte la tour.
+narrateur|Papa parle.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+papa|C'est ton tour.
+enfant-m|Une maison pour le ciel.
+maman|Oui.
+maman|Merci d'avoir attendu.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Victorino pose un cube, tout droit.
+narrateur|Un cube attrape un reflet de cacao.
+narrateur|On est encore dans la cuisine.
+maman|On attend.
+maman|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>cubes</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2430,7 +2538,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On lève la main. Chacun son tour.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2594,7 +2702,10 @@
       <c r="AV9" s="2" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On lève la main.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2622,7 +2733,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le matin. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la cuisine, les cubes et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>Le matin, la lumière est claire. Le cacao sent encore le chocolat. Les oiseaux parlent déjà, tout loin. Victorino a encore les cubes, dans la cuisine. Un cube jaune attrape le soleil sur la table. J'écoute encore un peu. Victorino lève la main. Il attend. Ma tour est jaune, comme le cacao. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Victorino range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2762,10 +2873,29 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le matin. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la cuisine, les cubes et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr"/>
+          <t>narrateur|Le matin, la lumière est claire.
+narrateur|Le cacao sent encore le chocolat.
+narrateur|Les oiseaux parlent déjà, tout loin.
+narrateur|Victorino a encore les cubes, dans la cuisine.
+narrateur|Un cube jaune attrape le soleil sur la table.
+papa|J'écoute encore un peu.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|Ma tour est jaune, comme le cacao.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Victorino range les cubes, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2790,7 +2920,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorino a vécu le matin, dans la cuisine. Il a joué avec les cubes. Bravo, Victorino. C'est du bon travail. Bonne journée, mon grand. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2930,7 +3060,15 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorino a vécu le matin, dans la cuisine.
+narrateur|Il a joué avec les cubes.
+papa|Bravo, Victorino.
+papa|C'est du bon travail.
+maman|Bonne journée, mon grand.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2958,7 +3096,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint après la sieste. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les joues sont chaudes. La couverture a un pli, tout doux. La maison est calme, encore un peu. Victorino a encore les cubes, dans la cuisine. Un cube fait un clic, tout petit, près des tasses. J'écoute encore un peu. Victorino lève la main. Il attend. Le cube est chaud, près de moi. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Victorino range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3098,7 +3236,22 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint après la sieste. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les joues sont chaudes.
+narrateur|La couverture a un pli, tout doux.
+narrateur|La maison est calme, encore un peu.
+narrateur|Victorino a encore les cubes, dans la cuisine.
+narrateur|Un cube fait un clic, tout petit, près des tasses.
+papa|J'écoute encore un peu.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|Le cube est chaud, près de moi.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Victorino range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3126,7 +3279,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorino a vécu après la sieste, dans la cuisine. Il a joué avec les cubes. Bravo, Victorino. C'est du bon travail. Bonne journée, mon grand. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3266,7 +3419,15 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorino a vécu après la sieste, dans la cuisine.
+narrateur|Il a joué avec les cubes.
+papa|Bravo, Victorino.
+papa|C'est du bon travail.
+maman|Bonne journée, mon grand.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3294,7 +3455,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le soir. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, les cubes et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>Le soir, la lampe fait un rond. Ça sent le pain, tout chaud. Les chaussons font toc, sur le bois. Victorino a encore les cubes, dans la cuisine. La lampe allonge l'ombre des cubes. J'écoute encore un peu. Victorino lève la main. Il attend. L'ombre des cubes est longue. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Victorino range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3434,10 +3595,29 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le soir. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, les cubes et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les chaussons font toc, sur le bois.
+narrateur|Victorino a encore les cubes, dans la cuisine.
+narrateur|La lampe allonge l'ombre des cubes.
+papa|J'écoute encore un peu.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|L'ombre des cubes est longue.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Victorino range les cubes, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3462,7 +3642,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorino a vécu le soir, dans la cuisine. Il a joué avec les cubes. Bravo, Victorino. C'est du bon travail. Bonne journée, mon grand. La lampe reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3602,7 +3782,15 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorino a vécu le soir, dans la cuisine.
+narrateur|Il a joué avec les cubes.
+papa|Bravo, Victorino.
+papa|C'est du bon travail.
+maman|Bonne journée, mon grand.
+narrateur|La lampe reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3630,7 +3818,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On montre du doigt, sans courir. maman n'est pas loin.</t>
+          <t>Victorino ouvre le livre. La page sent le papier, un peu sec. Un dessin de flaque est là, toute bleue. Moi, je lis d'abord. Maman lit jusqu'au bout. Victorino lève la main. Il attend. La flaque a un nuage. Oui. C'est ton tour. On a attendu. Puis on parle. Victorino caresse la page, tout léger. Bravo, Victorino. Une miette de pain reste au bord de la page. On est encore dans la cuisine. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3770,10 +3958,31 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On montre du doigt, sans courir. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr"/>
+          <t>narrateur|Victorino ouvre le livre.
+narrateur|La page sent le papier, un peu sec.
+narrateur|Un dessin de flaque est là, toute bleue.
+maman|Moi, je lis d'abord.
+narrateur|Maman lit jusqu'au bout.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|La flaque a un nuage.
+papa|Oui.
+papa|C'est ton tour.
+papa|On a attendu.
+papa|Puis on parle.
+narrateur|Victorino caresse la page, tout léger.
+maman|Bravo, Victorino.
+narrateur|Une miette de pain reste au bord de la page.
+narrateur|On est encore dans la cuisine.
+maman|On attend.
+maman|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3798,7 +4007,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On lève la main. Chacun son tour.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3962,7 +4171,10 @@
       <c r="AV17" s="2" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On lève la main.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -3990,7 +4202,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le matin. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la cuisine, le livre et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>Le matin, la lumière est claire. Le cacao sent encore le chocolat. Les oiseaux parlent déjà, tout loin. Victorino a encore le livre, dans la cuisine. Une miette reste collée sur la page. J'écoute encore un peu. Victorino lève la main. Il attend. La flaque du livre a un nuage. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Victorino range le livre, tout doux.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4130,10 +4342,29 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le matin. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la cuisine, le livre et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr"/>
+          <t>narrateur|Le matin, la lumière est claire.
+narrateur|Le cacao sent encore le chocolat.
+narrateur|Les oiseaux parlent déjà, tout loin.
+narrateur|Victorino a encore le livre, dans la cuisine.
+narrateur|Une miette reste collée sur la page.
+papa|J'écoute encore un peu.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|La flaque du livre a un nuage.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Victorino range le livre, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4158,7 +4389,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorino a vécu le matin, dans la cuisine. Il a joué avec le livre. Bravo, Victorino. C'est du bon travail. Bonne journée, mon grand. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4298,7 +4529,15 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorino a vécu le matin, dans la cuisine.
+narrateur|Il a joué avec le livre.
+papa|Bravo, Victorino.
+papa|C'est du bon travail.
+maman|Bonne journée, mon grand.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4326,7 +4565,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint après la sieste. La couverture est douce. On souffle doucement. Cette fin-là est celle de la cuisine, le livre et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les joues sont chaudes. La couverture a un pli, tout doux. La maison est calme, encore un peu. Victorino a encore le livre, dans la cuisine. Le livre est un peu chaud, comme la nappe. J'écoute encore un peu. Victorino lève la main. Il attend. La page est tiède. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Victorino range le livre, tout doux.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4466,7 +4705,22 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint après la sieste. La couverture est douce. On souffle doucement. Cette fin-là est celle de la cuisine, le livre et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les joues sont chaudes.
+narrateur|La couverture a un pli, tout doux.
+narrateur|La maison est calme, encore un peu.
+narrateur|Victorino a encore le livre, dans la cuisine.
+narrateur|Le livre est un peu chaud, comme la nappe.
+papa|J'écoute encore un peu.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|La page est tiède.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Victorino range le livre, tout doux.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4494,7 +4748,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorino a vécu après la sieste, dans la cuisine. Il a joué avec le livre. Bravo, Victorino. C'est du bon travail. Bonne journée, mon grand. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4634,7 +4888,15 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorino a vécu après la sieste, dans la cuisine.
+narrateur|Il a joué avec le livre.
+papa|Bravo, Victorino.
+papa|C'est du bon travail.
+maman|Bonne journée, mon grand.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4662,7 +4924,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le soir. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, le livre et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>Le soir, la lampe fait un rond. Ça sent le pain, tout chaud. Les chaussons font toc, sur le bois. Victorino a encore le livre, dans la cuisine. La flaque du livre brille sous la lampe. J'écoute encore un peu. Victorino lève la main. Il attend. La lampe lit avec nous. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Victorino range le livre, tout doux.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4802,10 +5064,29 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le soir. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, le livre et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les chaussons font toc, sur le bois.
+narrateur|Victorino a encore le livre, dans la cuisine.
+narrateur|La flaque du livre brille sous la lampe.
+papa|J'écoute encore un peu.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|La lampe lit avec nous.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Victorino range le livre, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4830,7 +5111,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorino a vécu le soir, dans la cuisine. Il a joué avec le livre. Bravo, Victorino. C'est du bon travail. Bonne journée, mon grand. La lampe reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4970,7 +5251,15 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorino a vécu le soir, dans la cuisine.
+narrateur|Il a joué avec le livre.
+papa|Bravo, Victorino.
+papa|C'est du bon travail.
+maman|Bonne journée, mon grand.
+narrateur|La lampe reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -4998,7 +5287,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On rit un peu. maman n'est pas loin.</t>
+          <t>Victorino prend la dînette. Une petite tasse sonne, tout creux. Une cuillère miniature est encore tiède. Moi, je sers le cacao imaginaire. Papa parle. Victorino lève la main. Il attend. Une tasse pour le moineau ? Oui. C'est ton tour. On attend. Puis on parle. Bravo. Tu as attendu ton tour. Victorino pose la petite tasse, tout doux. La petite tasse est près des vraies tasses. On est encore dans la cuisine. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5138,10 +5427,32 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On rit un peu. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr"/>
+          <t>narrateur|Victorino prend la dînette.
+narrateur|Une petite tasse sonne, tout creux.
+narrateur|Une cuillère miniature est encore tiède.
+papa|Moi, je sers le cacao imaginaire.
+narrateur|Papa parle.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|Une tasse pour le moineau ?
+maman|Oui.
+maman|C'est ton tour.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo.
+papa|Tu as attendu ton tour.
+narrateur|Victorino pose la petite tasse, tout doux.
+narrateur|La petite tasse est près des vraies tasses.
+narrateur|On est encore dans la cuisine.
+maman|On attend.
+maman|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>tasse</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5166,7 +5477,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On lève la main. Chacun son tour.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5330,7 +5641,10 @@
       <c r="AV25" s="2" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On lève la main.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5358,7 +5672,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le matin. La couverture est douce. On dit merci. Cette fin-là est celle de la cuisine, la dînette et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>Le matin, la lumière est claire. Le cacao sent encore le chocolat. Les oiseaux parlent déjà, tout loin. Victorino a encore la dînette, dans la cuisine. La petite tasse sent encore le cacao. J'écoute encore un peu. Victorino lève la main. Il attend. Le cacao imaginaire est chaud. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Victorino range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5498,10 +5812,29 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le matin. La couverture est douce. On dit merci. Cette fin-là est celle de la cuisine, la dînette et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr"/>
+          <t>narrateur|Le matin, la lumière est claire.
+narrateur|Le cacao sent encore le chocolat.
+narrateur|Les oiseaux parlent déjà, tout loin.
+narrateur|Victorino a encore la dînette, dans la cuisine.
+narrateur|La petite tasse sent encore le cacao.
+papa|J'écoute encore un peu.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|Le cacao imaginaire est chaud.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Victorino range la dînette, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5526,7 +5859,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorino a vécu le matin, dans la cuisine. Il a joué avec la dînette. Bravo, Victorino. C'est du bon travail. Bonne journée, mon grand. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5666,7 +5999,15 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorino a vécu le matin, dans la cuisine.
+narrateur|Il a joué avec la dînette.
+papa|Bravo, Victorino.
+papa|C'est du bon travail.
+maman|Bonne journée, mon grand.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5694,7 +6035,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint après la sieste. On entend un oiseau. On souffle doucement. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les joues sont chaudes. La couverture a un pli, tout doux. La maison est calme, encore un peu. Victorino a encore la dînette, dans la cuisine. Une cuillère miniature tremble près du bol. J'écoute encore un peu. Victorino lève la main. Il attend. La petite tasse a dormi. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Victorino range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5834,7 +6175,22 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint après la sieste. On entend un oiseau. On souffle doucement. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les joues sont chaudes.
+narrateur|La couverture a un pli, tout doux.
+narrateur|La maison est calme, encore un peu.
+narrateur|Victorino a encore la dînette, dans la cuisine.
+narrateur|Une cuillère miniature tremble près du bol.
+papa|J'écoute encore un peu.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|La petite tasse a dormi.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Victorino range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5862,7 +6218,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorino a vécu après la sieste, dans la cuisine. Il a joué avec la dînette. Bravo, Victorino. C'est du bon travail. Bonne journée, mon grand. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6002,7 +6358,15 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorino a vécu après la sieste, dans la cuisine.
+narrateur|Il a joué avec la dînette.
+papa|Bravo, Victorino.
+papa|C'est du bon travail.
+maman|Bonne journée, mon grand.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6030,7 +6394,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le soir. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, la dînette et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>Le soir, la lampe fait un rond. Ça sent le pain, tout chaud. Les chaussons font toc, sur le bois. Victorino a encore la dînette, dans la cuisine. La dînette fait un tout petit ding. J'écoute encore un peu. Victorino lève la main. Il attend. La dînette fait ding. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Victorino range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6170,10 +6534,29 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le soir. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, la dînette et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les chaussons font toc, sur le bois.
+narrateur|Victorino a encore la dînette, dans la cuisine.
+narrateur|La dînette fait un tout petit ding.
+papa|J'écoute encore un peu.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|La dînette fait ding.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Victorino range la dînette, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6198,7 +6581,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorino a vécu le soir, dans la cuisine. Il a joué avec la dînette. Bravo, Victorino. C'est du bon travail. Bonne journée, mon grand. La lampe reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6338,7 +6721,15 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorino a vécu le soir, dans la cuisine.
+narrateur|Il a joué avec la dînette.
+papa|Bravo, Victorino.
+papa|C'est du bon travail.
+maman|Bonne journée, mon grand.
+narrateur|La lampe reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6366,7 +6757,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Jules va vers le jardin. L'eau coule, tout petit bruit. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Jules se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On souffle doucement. Je suis là. On reste ensemble.</t>
+          <t>Victorino pose un pied dans l'herbe. L'herbe est froide, encore brillante. Un chaussette danse sur le fil. La flaque sous la boîte tremble. Moi, je raconte le moineau. Maman parle jusqu'au bout. Victorino lève la main. Il attend. Le ciel est dans l'eau. Oui. Merci d'avoir attendu. On attend. Puis on parle. Victorino se penche, tout doux. Un moineau picore près du portail. Bravo, Victorino. Tu as levé la main.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6506,11 +6897,30 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Jules va vers le jardin. L'eau coule, tout petit bruit. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Jules se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On souffle doucement.
-papa|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr"/>
+          <t>narrateur|Victorino pose un pied dans l'herbe.
+narrateur|L'herbe est froide, encore brillante.
+narrateur|Un chaussette danse sur le fil.
+narrateur|La flaque sous la boîte tremble.
+maman|Moi, je raconte le moineau.
+narrateur|Maman parle jusqu'au bout.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|Le ciel est dans l'eau.
+papa|Oui.
+papa|Merci d'avoir attendu.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Victorino se penche, tout doux.
+narrateur|Un moineau picore près du portail.
+maman|Bravo, Victorino.
+maman|Tu as levé la main.</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>oiseau,herbe</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6535,7 +6945,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Tour de parole.</t>
+          <t>Victorino lève la main, dans l'herbe. Et après, on attend ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6691,7 +7101,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Tour de parole.</t>
+          <t>narrateur|Victorino lève la main, dans l'herbe.
+maman|Et après, on attend ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6719,7 +7130,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : lever la main ; attendre. Jules respire. Jules retient : attendre, puis parler. On continue, avec papa.</t>
+          <t>Oui. On attend. Puis on parle. Victorino essuie une goutte sur son genou. J'attends mon tour. Bravo, Victorino. La flaque est à toi, et le tour aussi. Tu as levé la main ? Oui.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6863,7 +7274,15 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : lever la main ; attendre. Jules respire. Jules retient : attendre, puis parler. On continue, avec papa.</t>
+          <t>maman|Oui.
+maman|On attend.
+maman|Puis on parle.
+narrateur|Victorino essuie une goutte sur son genou.
+enfant-m|J'attends mon tour.
+papa|Bravo, Victorino.
+papa|La flaque est à toi, et le tour aussi.
+maman|Tu as levé la main ?
+enfant-m|Oui.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6891,7 +7310,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Trois jeux attendent, tout proches. Les cubes, le livre, ou la dînette ? On joue. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7055,7 +7474,11 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Trois jeux attendent, tout proches.
+maman|Les cubes, le livre, ou la dînette ?
+papa|On joue.
+papa|On attend.
+papa|Puis on parle.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7083,7 +7506,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi les cubes. Un chat miaule une fois. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On attend son tour. maman n'est pas loin.</t>
+          <t>Victorino prend les cubes en bois. Un cube rouge fait clic. Un cube jaune sent le pin. Moi, je raconte la tour. Papa parle. Victorino lève la main. Il attend. C'est ton tour. Une maison pour le ciel. Oui. Merci d'avoir attendu. On attend. Puis on parle. Victorino pose un cube, tout droit. L'herbe mouille un cube, tout vert. On est encore dans le jardin. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7223,10 +7646,31 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi les cubes. Un chat miaule une fois. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On attend son tour. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr"/>
+          <t>narrateur|Victorino prend les cubes en bois.
+narrateur|Un cube rouge fait clic.
+narrateur|Un cube jaune sent le pin.
+papa|Moi, je raconte la tour.
+narrateur|Papa parle.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+papa|C'est ton tour.
+enfant-m|Une maison pour le ciel.
+maman|Oui.
+maman|Merci d'avoir attendu.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Victorino pose un cube, tout droit.
+narrateur|L'herbe mouille un cube, tout vert.
+narrateur|On est encore dans le jardin.
+maman|On attend.
+maman|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>cubes</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7251,7 +7695,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On lève la main. Chacun son tour.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7415,7 +7859,10 @@
       <c r="AV37" s="2" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On lève la main.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7443,7 +7890,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le matin. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>Le matin, la lumière est claire. Le cacao sent encore le chocolat. Les oiseaux parlent déjà, tout loin. Victorino a encore les cubes, dans le jardin. L'herbe mouille un cube, tout vert. J'écoute encore un peu. Victorino lève la main. Il attend. Le cube a de l'herbe. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Victorino range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7583,10 +8030,29 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le matin. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr"/>
+          <t>narrateur|Le matin, la lumière est claire.
+narrateur|Le cacao sent encore le chocolat.
+narrateur|Les oiseaux parlent déjà, tout loin.
+narrateur|Victorino a encore les cubes, dans le jardin.
+narrateur|L'herbe mouille un cube, tout vert.
+papa|J'écoute encore un peu.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|Le cube a de l'herbe.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Victorino range les cubes, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7611,7 +8077,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorino a vécu le matin, dans le jardin. Il a joué avec les cubes. Bravo, Victorino. C'est du bon travail. Bonne journée, mon grand. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7751,7 +8217,15 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorino a vécu le matin, dans le jardin.
+narrateur|Il a joué avec les cubes.
+papa|Bravo, Victorino.
+papa|C'est du bon travail.
+maman|Bonne journée, mon grand.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7779,7 +8253,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint après la sieste. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, les cubes et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les joues sont chaudes. La couverture a un pli, tout doux. La maison est calme, encore un peu. Victorino a encore les cubes, dans le jardin. Un cube sèche au soleil, près de la flaque. J'écoute encore un peu. Victorino lève la main. Il attend. Le cube sèche, tout seul. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Victorino range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7919,7 +8393,22 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint après la sieste. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, les cubes et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les joues sont chaudes.
+narrateur|La couverture a un pli, tout doux.
+narrateur|La maison est calme, encore un peu.
+narrateur|Victorino a encore les cubes, dans le jardin.
+narrateur|Un cube sèche au soleil, près de la flaque.
+papa|J'écoute encore un peu.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|Le cube sèche, tout seul.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Victorino range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7947,7 +8436,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorino a vécu après la sieste, dans le jardin. Il a joué avec les cubes. Bravo, Victorino. C'est du bon travail. Bonne journée, mon grand. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8087,7 +8576,15 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorino a vécu après la sieste, dans le jardin.
+narrateur|Il a joué avec les cubes.
+papa|Bravo, Victorino.
+papa|C'est du bon travail.
+maman|Bonne journée, mon grand.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8115,7 +8612,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le soir. On entend un oiseau. On attend son tour. Cette fin-là est celle de le jardin, les cubes et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>Le soir, la lampe fait un rond. Ça sent le pain, tout chaud. Les chaussons font toc, sur le bois. Victorino a encore les cubes, dans le jardin. Un cube garde une goutte, toute ronde. J'écoute encore un peu. Victorino lève la main. Il attend. Le cube a une goutte. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Victorino range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8255,10 +8752,29 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le soir. On entend un oiseau. On attend son tour. Cette fin-là est celle de le jardin, les cubes et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les chaussons font toc, sur le bois.
+narrateur|Victorino a encore les cubes, dans le jardin.
+narrateur|Un cube garde une goutte, toute ronde.
+papa|J'écoute encore un peu.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|Le cube a une goutte.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Victorino range les cubes, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8283,7 +8799,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorino a vécu le soir, dans le jardin. Il a joué avec les cubes. Bravo, Victorino. C'est du bon travail. Bonne journée, mon grand. La lampe reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8423,7 +8939,15 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorino a vécu le soir, dans le jardin.
+narrateur|Il a joué avec les cubes.
+papa|Bravo, Victorino.
+papa|C'est du bon travail.
+maman|Bonne journée, mon grand.
+narrateur|La lampe reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8451,7 +8975,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi le livre. Les chaussures font toc toc. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On montre du doigt, sans courir. maman n'est pas loin.</t>
+          <t>Victorino ouvre le livre. La page sent le papier, un peu sec. Un dessin de flaque est là, toute bleue. Moi, je lis d'abord. Maman lit jusqu'au bout. Victorino lève la main. Il attend. La flaque a un nuage. Oui. C'est ton tour. On a attendu. Puis on parle. Victorino caresse la page, tout léger. Bravo, Victorino. Une vraie feuille sert de marque-page. On est encore dans le jardin. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8591,10 +9115,31 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi le livre. Les chaussures font toc toc. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On montre du doigt, sans courir. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr"/>
+          <t>narrateur|Victorino ouvre le livre.
+narrateur|La page sent le papier, un peu sec.
+narrateur|Un dessin de flaque est là, toute bleue.
+maman|Moi, je lis d'abord.
+narrateur|Maman lit jusqu'au bout.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|La flaque a un nuage.
+papa|Oui.
+papa|C'est ton tour.
+papa|On a attendu.
+papa|Puis on parle.
+narrateur|Victorino caresse la page, tout léger.
+maman|Bravo, Victorino.
+narrateur|Une vraie feuille sert de marque-page.
+narrateur|On est encore dans le jardin.
+maman|On attend.
+maman|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8619,7 +9164,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On lève la main. Chacun son tour.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8783,7 +9328,10 @@
       <c r="AV45" s="2" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On lève la main.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8811,7 +9359,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le matin. La couverture est douce. On souffle doucement. Cette fin-là est celle de le jardin, le livre et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>Le matin, la lumière est claire. Le cacao sent encore le chocolat. Les oiseaux parlent déjà, tout loin. Victorino a encore le livre, dans le jardin. Une feuille vraie marque encore la page. J'écoute encore un peu. Victorino lève la main. Il attend. Une vraie feuille est dans le livre. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Victorino range le livre, tout doux.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8951,10 +9499,29 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le matin. La couverture est douce. On souffle doucement. Cette fin-là est celle de le jardin, le livre et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr"/>
+          <t>narrateur|Le matin, la lumière est claire.
+narrateur|Le cacao sent encore le chocolat.
+narrateur|Les oiseaux parlent déjà, tout loin.
+narrateur|Victorino a encore le livre, dans le jardin.
+narrateur|Une feuille vraie marque encore la page.
+papa|J'écoute encore un peu.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|Une vraie feuille est dans le livre.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Victorino range le livre, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8979,7 +9546,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorino a vécu le matin, dans le jardin. Il a joué avec le livre. Bravo, Victorino. C'est du bon travail. Bonne journée, mon grand. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9119,7 +9686,15 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorino a vécu le matin, dans le jardin.
+narrateur|Il a joué avec le livre.
+papa|Bravo, Victorino.
+papa|C'est du bon travail.
+maman|Bonne journée, mon grand.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9147,7 +9722,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint après la sieste. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, le livre et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les joues sont chaudes. La couverture a un pli, tout doux. La maison est calme, encore un peu. Victorino a encore le livre, dans le jardin. Le livre sent l'herbe, un peu. J'écoute encore un peu. Victorino lève la main. Il attend. Le livre sent l'herbe. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Victorino range le livre, tout doux.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9287,7 +9862,22 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint après la sieste. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, le livre et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les joues sont chaudes.
+narrateur|La couverture a un pli, tout doux.
+narrateur|La maison est calme, encore un peu.
+narrateur|Victorino a encore le livre, dans le jardin.
+narrateur|Le livre sent l'herbe, un peu.
+papa|J'écoute encore un peu.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|Le livre sent l'herbe.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Victorino range le livre, tout doux.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9315,7 +9905,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorino a vécu après la sieste, dans le jardin. Il a joué avec le livre. Bravo, Victorino. C'est du bon travail. Bonne journée, mon grand. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9455,7 +10045,15 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorino a vécu après la sieste, dans le jardin.
+narrateur|Il a joué avec le livre.
+papa|Bravo, Victorino.
+papa|C'est du bon travail.
+maman|Bonne journée, mon grand.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9483,7 +10081,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le soir. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de le jardin, le livre et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>Le soir, la lampe fait un rond. Ça sent le pain, tout chaud. Les chaussons font toc, sur le bois. Victorino a encore le livre, dans le jardin. Un oiseau chante. J'écoute encore un peu. Victorino lève la main. Il attend. L'oiseau a fini sa phrase. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Victorino range le livre, tout doux.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9623,10 +10221,29 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le soir. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de le jardin, le livre et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les chaussons font toc, sur le bois.
+narrateur|Victorino a encore le livre, dans le jardin.
+narrateur|Un oiseau chante.
+papa|J'écoute encore un peu.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|L'oiseau a fini sa phrase.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Victorino range le livre, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9651,7 +10268,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorino a vécu le soir, dans le jardin. Il a joué avec le livre. Bravo, Victorino. C'est du bon travail. Bonne journée, mon grand. La lampe reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9791,7 +10408,15 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorino a vécu le soir, dans le jardin.
+narrateur|Il a joué avec le livre.
+papa|Bravo, Victorino.
+papa|C'est du bon travail.
+maman|Bonne journée, mon grand.
+narrateur|La lampe reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9819,7 +10444,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi la dînette. La couverture est douce. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On rit un peu. maman n'est pas loin.</t>
+          <t>Victorino prend la dînette. Une petite tasse sonne, tout creux. Une cuillère miniature est encore tiède. Moi, je sers le cacao imaginaire. Papa parle. Victorino lève la main. Il attend. Une tasse pour le moineau ? Oui. C'est ton tour. On attend. Puis on parle. Bravo. Tu as attendu ton tour. Victorino pose la petite tasse, tout doux. Une goutte perle au bord de la tasse. On est encore dans le jardin. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9959,10 +10584,32 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi la dînette. La couverture est douce. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On rit un peu. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr"/>
+          <t>narrateur|Victorino prend la dînette.
+narrateur|Une petite tasse sonne, tout creux.
+narrateur|Une cuillère miniature est encore tiède.
+papa|Moi, je sers le cacao imaginaire.
+narrateur|Papa parle.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|Une tasse pour le moineau ?
+maman|Oui.
+maman|C'est ton tour.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo.
+papa|Tu as attendu ton tour.
+narrateur|Victorino pose la petite tasse, tout doux.
+narrateur|Une goutte perle au bord de la tasse.
+narrateur|On est encore dans le jardin.
+maman|On attend.
+maman|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>tasse</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9987,7 +10634,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On lève la main. Chacun son tour.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10151,7 +10798,10 @@
       <c r="AV53" s="2" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On lève la main.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10179,7 +10829,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le matin. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>Le matin, la lumière est claire. Le cacao sent encore le chocolat. Les oiseaux parlent déjà, tout loin. Victorino a encore la dînette, dans le jardin. Une petite tasse a une goutte de rosée. J'écoute encore un peu. Victorino lève la main. Il attend. La rosée est dans la tasse. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Victorino range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10319,10 +10969,29 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le matin. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr"/>
+          <t>narrateur|Le matin, la lumière est claire.
+narrateur|Le cacao sent encore le chocolat.
+narrateur|Les oiseaux parlent déjà, tout loin.
+narrateur|Victorino a encore la dînette, dans le jardin.
+narrateur|Une petite tasse a une goutte de rosée.
+papa|J'écoute encore un peu.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|La rosée est dans la tasse.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Victorino range la dînette, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10347,7 +11016,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorino a vécu le matin, dans le jardin. Il a joué avec la dînette. Bravo, Victorino. C'est du bon travail. Bonne journée, mon grand. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10487,7 +11156,15 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorino a vécu le matin, dans le jardin.
+narrateur|Il a joué avec la dînette.
+papa|Bravo, Victorino.
+papa|C'est du bon travail.
+maman|Bonne journée, mon grand.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10515,7 +11192,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint après la sieste. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, la dînette et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les joues sont chaudes. La couverture a un pli, tout doux. La maison est calme, encore un peu. Victorino a encore la dînette, dans le jardin. La dînette est tiède, au soleil. J'écoute encore un peu. Victorino lève la main. Il attend. La tasse est tiède. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Victorino range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10655,7 +11332,22 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint après la sieste. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, la dînette et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les joues sont chaudes.
+narrateur|La couverture a un pli, tout doux.
+narrateur|La maison est calme, encore un peu.
+narrateur|Victorino a encore la dînette, dans le jardin.
+narrateur|La dînette est tiède, au soleil.
+papa|J'écoute encore un peu.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|La tasse est tiède.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Victorino range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10683,7 +11375,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorino a vécu après la sieste, dans le jardin. Il a joué avec la dînette. Bravo, Victorino. C'est du bon travail. Bonne journée, mon grand. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10823,7 +11515,15 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorino a vécu après la sieste, dans le jardin.
+narrateur|Il a joué avec la dînette.
+papa|Bravo, Victorino.
+papa|C'est du bon travail.
+maman|Bonne journée, mon grand.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10851,7 +11551,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le soir. Le vent est doux. On attend son tour. Cette fin-là est celle de le jardin, la dînette et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>Le soir, la lampe fait un rond. Ça sent le pain, tout chaud. Les chaussons font toc, sur le bois. Victorino a encore la dînette, dans le jardin. Loin de la dînette, la flaque tient encore le ciel. J'écoute encore un peu. Victorino lève la main. Il attend. La flaque tient encore le ciel. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Victorino range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -10991,10 +11691,29 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le soir. Le vent est doux. On attend son tour. Cette fin-là est celle de le jardin, la dînette et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les chaussons font toc, sur le bois.
+narrateur|Victorino a encore la dînette, dans le jardin.
+narrateur|Loin de la dînette, la flaque tient encore le ciel.
+papa|J'écoute encore un peu.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|La flaque tient encore le ciel.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Victorino range la dînette, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11019,7 +11738,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorino a vécu le soir, dans le jardin. Il a joué avec la dînette. Bravo, Victorino. C'est du bon travail. Bonne journée, mon grand. La lampe reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11159,7 +11878,15 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorino a vécu le soir, dans le jardin.
+narrateur|Il a joué avec la dînette.
+papa|Bravo, Victorino.
+papa|C'est du bon travail.
+maman|Bonne journée, mon grand.
+narrateur|La lampe reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11187,7 +11914,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Jules va vers la chambre. Un vélo passe au loin. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Jules se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On écoute jusqu'au bout. Je suis là. On reste ensemble.</t>
+          <t>Victorino entre dans la chambre. La vitre est un peu embuée. Le cartable repose au pied du lit. Le doudou attend contre l'oreiller. Moi, je raconte le chemin. Papa parle, tout bas. Victorino lève la main. Il attend. Le chemin brille, derrière la vitre. C'est ton tour. On a attendu. Puis on parle. Bravo. Tu as levé la main. Le radiateur fait un petit tic. Un carré de ciel pose sur le parquet.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11327,11 +12054,29 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Jules va vers la chambre. Un vélo passe au loin. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Jules se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On écoute jusqu'au bout.
-papa|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr"/>
+          <t>narrateur|Victorino entre dans la chambre.
+narrateur|La vitre est un peu embuée.
+narrateur|Le cartable repose au pied du lit.
+narrateur|Le doudou attend contre l'oreiller.
+papa|Moi, je raconte le chemin.
+narrateur|Papa parle, tout bas.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|Le chemin brille, derrière la vitre.
+maman|C'est ton tour.
+maman|On a attendu.
+maman|Puis on parle.
+papa|Bravo.
+papa|Tu as levé la main.
+narrateur|Le radiateur fait un petit tic.
+narrateur|Un carré de ciel pose sur le parquet.</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>radiateur</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11356,7 +12101,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Tour de parole.</t>
+          <t>Chacun son tour, près du doudou. On attend, puis on parle ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11512,7 +12257,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Tour de parole.</t>
+          <t>narrateur|Chacun son tour, près du doudou.
+papa|On attend, puis on parle ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11540,7 +12286,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : lever la main ; attendre. Jules respire. Jules retient : attendre, puis parler. On continue, avec papa.</t>
+          <t>Oui. On lève la main. On attend. Puis on parle. Victorino hoche la tête. Chacun son tour. On continue, tout doux. Tu as levé la main. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11684,7 +12430,15 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : lever la main ; attendre. Jules respire. Jules retient : attendre, puis parler. On continue, avec papa.</t>
+          <t>papa|Oui.
+papa|On lève la main.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Victorino hoche la tête.
+enfant-m|Chacun son tour.
+maman|On continue, tout doux.
+maman|Tu as levé la main.
+papa|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11712,7 +12466,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Trois jeux attendent, tout proches. Les cubes, le livre, ou la dînette ? On joue. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11876,7 +12630,11 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Trois jeux attendent, tout proches.
+maman|Les cubes, le livre, ou la dînette ?
+papa|On joue.
+papa|On attend.
+papa|Puis on parle.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11904,7 +12662,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On attend son tour. maman n'est pas loin.</t>
+          <t>Victorino prend les cubes en bois. Un cube rouge fait clic. Un cube jaune sent le pin. Moi, je raconte la tour. Papa parle. Victorino lève la main. Il attend. C'est ton tour. Une maison pour le ciel. Oui. Merci d'avoir attendu. On attend. Puis on parle. Victorino pose un cube, tout droit. Un cube tapote le parquet, tout doux. On est encore dans la chambre. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12044,10 +12802,31 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On attend son tour. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr"/>
+          <t>narrateur|Victorino prend les cubes en bois.
+narrateur|Un cube rouge fait clic.
+narrateur|Un cube jaune sent le pin.
+papa|Moi, je raconte la tour.
+narrateur|Papa parle.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+papa|C'est ton tour.
+enfant-m|Une maison pour le ciel.
+maman|Oui.
+maman|Merci d'avoir attendu.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Victorino pose un cube, tout droit.
+narrateur|Un cube tapote le parquet, tout doux.
+narrateur|On est encore dans la chambre.
+maman|On attend.
+maman|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>cubes</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12072,7 +12851,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On lève la main. Chacun son tour.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12236,7 +13015,10 @@
       <c r="AV65" s="2" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On lève la main.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12264,7 +13046,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le matin. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>Le matin, la lumière est claire. Le cacao sent encore le chocolat. Les oiseaux parlent déjà, tout loin. Victorino a encore les cubes, dans la chambre. Un rayon pose sur la tour de cubes. J'écoute encore un peu. Victorino lève la main. Il attend. Le soleil est sur ma tour. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Victorino range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12404,10 +13186,29 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le matin. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr"/>
+          <t>narrateur|Le matin, la lumière est claire.
+narrateur|Le cacao sent encore le chocolat.
+narrateur|Les oiseaux parlent déjà, tout loin.
+narrateur|Victorino a encore les cubes, dans la chambre.
+narrateur|Un rayon pose sur la tour de cubes.
+papa|J'écoute encore un peu.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|Le soleil est sur ma tour.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Victorino range les cubes, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12432,7 +13233,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorino a vécu le matin, dans la chambre. Il a joué avec les cubes. Bravo, Victorino. C'est du bon travail. Bonne journée, mon grand. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12572,7 +13373,15 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorino a vécu le matin, dans la chambre.
+narrateur|Il a joué avec les cubes.
+papa|Bravo, Victorino.
+papa|C'est du bon travail.
+maman|Bonne journée, mon grand.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12600,7 +13409,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint après la sieste. On entend un oiseau. On attend son tour. Cette fin-là est celle de la chambre, les cubes et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les joues sont chaudes. La couverture a un pli, tout doux. La maison est calme, encore un peu. Victorino a encore les cubes, dans la chambre. Un cube est contre l'oreiller, tout calme. J'écoute encore un peu. Victorino lève la main. Il attend. Le cube a dormi aussi. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Victorino range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12740,7 +13549,22 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint après la sieste. On entend un oiseau. On attend son tour. Cette fin-là est celle de la chambre, les cubes et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les joues sont chaudes.
+narrateur|La couverture a un pli, tout doux.
+narrateur|La maison est calme, encore un peu.
+narrateur|Victorino a encore les cubes, dans la chambre.
+narrateur|Un cube est contre l'oreiller, tout calme.
+papa|J'écoute encore un peu.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|Le cube a dormi aussi.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Victorino range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12768,7 +13592,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorino a vécu après la sieste, dans la chambre. Il a joué avec les cubes. Bravo, Victorino. C'est du bon travail. Bonne journée, mon grand. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12908,7 +13732,15 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorino a vécu après la sieste, dans la chambre.
+narrateur|Il a joué avec les cubes.
+papa|Bravo, Victorino.
+papa|C'est du bon travail.
+maman|Bonne journée, mon grand.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12936,7 +13768,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le soir. Ça sent le pain chaud. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, les cubes et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>Le soir, la lampe fait un rond. Ça sent le pain, tout chaud. Les chaussons font toc, sur le bois. Victorino a encore les cubes, dans la chambre. L'ombre des cubes danse sur le mur. J'écoute encore un peu. Victorino lève la main. Il attend. Les cubes dansent au mur. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Victorino range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13076,10 +13908,29 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le soir. Ça sent le pain chaud. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, les cubes et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les chaussons font toc, sur le bois.
+narrateur|Victorino a encore les cubes, dans la chambre.
+narrateur|L'ombre des cubes danse sur le mur.
+papa|J'écoute encore un peu.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|Les cubes dansent au mur.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Victorino range les cubes, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13104,7 +13955,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorino a vécu le soir, dans la chambre. Il a joué avec les cubes. Bravo, Victorino. C'est du bon travail. Bonne journée, mon grand. La lampe reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13244,7 +14095,15 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorino a vécu le soir, dans la chambre.
+narrateur|Il a joué avec les cubes.
+papa|Bravo, Victorino.
+papa|C'est du bon travail.
+maman|Bonne journée, mon grand.
+narrateur|La lampe reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13272,7 +14131,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On montre du doigt, sans courir. maman n'est pas loin.</t>
+          <t>Victorino ouvre le livre. La page sent le papier, un peu sec. Un dessin de flaque est là, toute bleue. Moi, je lis d'abord. Maman lit jusqu'au bout. Victorino lève la main. Il attend. La flaque a un nuage. Oui. C'est ton tour. On a attendu. Puis on parle. Victorino caresse la page, tout léger. Bravo, Victorino. La vitre embuée colore la page, tout pâle. On est encore dans la chambre. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13412,10 +14271,31 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On montre du doigt, sans courir. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr"/>
+          <t>narrateur|Victorino ouvre le livre.
+narrateur|La page sent le papier, un peu sec.
+narrateur|Un dessin de flaque est là, toute bleue.
+maman|Moi, je lis d'abord.
+narrateur|Maman lit jusqu'au bout.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|La flaque a un nuage.
+papa|Oui.
+papa|C'est ton tour.
+papa|On a attendu.
+papa|Puis on parle.
+narrateur|Victorino caresse la page, tout léger.
+maman|Bravo, Victorino.
+narrateur|La vitre embuée colore la page, tout pâle.
+narrateur|On est encore dans la chambre.
+maman|On attend.
+maman|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13440,7 +14320,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On lève la main. Chacun son tour.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13604,7 +14484,10 @@
       <c r="AV73" s="2" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On lève la main.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13632,7 +14515,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le matin. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>Le matin, la lumière est claire. Le cacao sent encore le chocolat. Les oiseaux parlent déjà, tout loin. Victorino a encore le livre, dans la chambre. La vitre filtre la page, tout pâle. J'écoute encore un peu. Victorino lève la main. Il attend. La vitre a un nuage, trop. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Victorino range le livre, tout doux.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13772,10 +14655,29 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le matin. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr"/>
+          <t>narrateur|Le matin, la lumière est claire.
+narrateur|Le cacao sent encore le chocolat.
+narrateur|Les oiseaux parlent déjà, tout loin.
+narrateur|Victorino a encore le livre, dans la chambre.
+narrateur|La vitre filtre la page, tout pâle.
+papa|J'écoute encore un peu.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|La vitre a un nuage, trop.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Victorino range le livre, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13800,7 +14702,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorino a vécu le matin, dans la chambre. Il a joué avec le livre. Bravo, Victorino. C'est du bon travail. Bonne journée, mon grand. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13940,7 +14842,15 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorino a vécu le matin, dans la chambre.
+narrateur|Il a joué avec le livre.
+papa|Bravo, Victorino.
+papa|C'est du bon travail.
+maman|Bonne journée, mon grand.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -13968,7 +14878,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint après la sieste. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de la chambre, le livre et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les joues sont chaudes. La couverture a un pli, tout doux. La maison est calme, encore un peu. Victorino a encore le livre, dans la chambre. Le livre est ouvert sur la couverture. J'écoute encore un peu. Victorino lève la main. Il attend. Le livre est sur la couverture. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Victorino range le livre, tout doux.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14108,7 +15018,22 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint après la sieste. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de la chambre, le livre et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les joues sont chaudes.
+narrateur|La couverture a un pli, tout doux.
+narrateur|La maison est calme, encore un peu.
+narrateur|Victorino a encore le livre, dans la chambre.
+narrateur|Le livre est ouvert sur la couverture.
+papa|J'écoute encore un peu.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|Le livre est sur la couverture.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Victorino range le livre, tout doux.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14136,7 +15061,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorino a vécu après la sieste, dans la chambre. Il a joué avec le livre. Bravo, Victorino. C'est du bon travail. Bonne journée, mon grand. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14276,7 +15201,15 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorino a vécu après la sieste, dans la chambre.
+narrateur|Il a joué avec le livre.
+papa|Bravo, Victorino.
+papa|C'est du bon travail.
+maman|Bonne journée, mon grand.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14304,7 +15237,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le soir. Le vent est doux. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, le livre et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>Le soir, la lampe fait un rond. Ça sent le pain, tout chaud. Les chaussons font toc, sur le bois. Victorino a encore le livre, dans la chambre. La page sent le doudou, un peu. J'écoute encore un peu. Victorino lève la main. Il attend. Le doudou écoute la page. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Victorino range le livre, tout doux.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14444,10 +15377,29 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le soir. Le vent est doux. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, le livre et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les chaussons font toc, sur le bois.
+narrateur|Victorino a encore le livre, dans la chambre.
+narrateur|La page sent le doudou, un peu.
+papa|J'écoute encore un peu.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|Le doudou écoute la page.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Victorino range le livre, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14472,7 +15424,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorino a vécu le soir, dans la chambre. Il a joué avec le livre. Bravo, Victorino. C'est du bon travail. Bonne journée, mon grand. La lampe reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14612,7 +15564,15 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorino a vécu le soir, dans la chambre.
+narrateur|Il a joué avec le livre.
+papa|Bravo, Victorino.
+papa|C'est du bon travail.
+maman|Bonne journée, mon grand.
+narrateur|La lampe reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14640,7 +15600,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On rit un peu. maman n'est pas loin.</t>
+          <t>Victorino prend la dînette. Une petite tasse sonne, tout creux. Une cuillère miniature est encore tiède. Moi, je sers le cacao imaginaire. Papa parle. Victorino lève la main. Il attend. Une tasse pour le moineau ? Oui. C'est ton tour. On attend. Puis on parle. Bravo. Tu as attendu ton tour. Victorino pose la petite tasse, tout doux. La petite tasse est près du doudou. On est encore dans la chambre. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14780,10 +15740,32 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : lever la main ; attendre. Jules répète tout bas : attendre, puis parler. On rit un peu. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr"/>
+          <t>narrateur|Victorino prend la dînette.
+narrateur|Une petite tasse sonne, tout creux.
+narrateur|Une cuillère miniature est encore tiède.
+papa|Moi, je sers le cacao imaginaire.
+narrateur|Papa parle.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|Une tasse pour le moineau ?
+maman|Oui.
+maman|C'est ton tour.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo.
+papa|Tu as attendu ton tour.
+narrateur|Victorino pose la petite tasse, tout doux.
+narrateur|La petite tasse est près du doudou.
+narrateur|On est encore dans la chambre.
+maman|On attend.
+maman|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>tasse</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14808,7 +15790,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On lève la main. Chacun son tour.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -14972,7 +15954,10 @@
       <c r="AV81" s="2" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On lève la main.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15000,7 +15985,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le matin. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>Le matin, la lumière est claire. Le cacao sent encore le chocolat. Les oiseaux parlent déjà, tout loin. Victorino a encore la dînette, dans la chambre. Une tasse miniature est près du lit. J'écoute encore un peu. Victorino lève la main. Il attend. La tasse est près du lit. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Victorino range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15140,10 +16125,29 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le matin. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et le matin. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr"/>
+          <t>narrateur|Le matin, la lumière est claire.
+narrateur|Le cacao sent encore le chocolat.
+narrateur|Les oiseaux parlent déjà, tout loin.
+narrateur|Victorino a encore la dînette, dans la chambre.
+narrateur|Une tasse miniature est près du lit.
+papa|J'écoute encore un peu.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|La tasse est près du lit.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Victorino range la dînette, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15168,7 +16172,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorino a vécu le matin, dans la chambre. Il a joué avec la dînette. Bravo, Victorino. C'est du bon travail. Bonne journée, mon grand. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15308,7 +16312,15 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorino a vécu le matin, dans la chambre.
+narrateur|Il a joué avec la dînette.
+papa|Bravo, Victorino.
+papa|C'est du bon travail.
+maman|Bonne journée, mon grand.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15336,7 +16348,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint après la sieste. Le vent est doux. On attend son tour. Cette fin-là est celle de la chambre, la dînette et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les joues sont chaudes. La couverture a un pli, tout doux. La maison est calme, encore un peu. Victorino a encore la dînette, dans la chambre. La dînette attend au pied du lit. J'écoute encore un peu. Victorino lève la main. Il attend. La dînette a attendu. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Victorino range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15476,7 +16488,22 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint après la sieste. Le vent est doux. On attend son tour. Cette fin-là est celle de la chambre, la dînette et après la sieste. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les joues sont chaudes.
+narrateur|La couverture a un pli, tout doux.
+narrateur|La maison est calme, encore un peu.
+narrateur|Victorino a encore la dînette, dans la chambre.
+narrateur|La dînette attend au pied du lit.
+papa|J'écoute encore un peu.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|La dînette a attendu.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Victorino range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15504,7 +16531,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorino a vécu après la sieste, dans la chambre. Il a joué avec la dînette. Bravo, Victorino. C'est du bon travail. Bonne journée, mon grand. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15644,7 +16671,15 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorino a vécu après la sieste, dans la chambre.
+narrateur|Il a joué avec la dînette.
+papa|Bravo, Victorino.
+papa|C'est du bon travail.
+maman|Bonne journée, mon grand.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15672,7 +16707,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le soir. Le sol est un peu froid. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, la dînette et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
+          <t>Le soir, la lampe fait un rond. Ça sent le pain, tout chaud. Les chaussons font toc, sur le bois. Victorino a encore la dînette, dans la chambre. Une petite tasse reflète la veilleuse. J'écoute encore un peu. Victorino lève la main. Il attend. La veilleuse est dans la tasse. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, partout. Merci, papa. Merci, maman. Victorino range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15812,10 +16847,29 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le soir. Le sol est un peu froid. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, la dînette et le soir. Jules a appris : Tour de parole. Voici le geste : lever la main ; attendre. Jules a entendu : attendre, puis parler. Jules dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les chaussons font toc, sur le bois.
+narrateur|Victorino a encore la dînette, dans la chambre.
+narrateur|Une petite tasse reflète la veilleuse.
+papa|J'écoute encore un peu.
+narrateur|Victorino lève la main.
+narrateur|Il attend.
+enfant-m|La veilleuse est dans la tasse.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, partout.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Victorino range la dînette, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15840,7 +16894,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorino a vécu le soir, dans la chambre. Il a joué avec la dînette. Bravo, Victorino. C'est du bon travail. Bonne journée, mon grand. La lampe reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -15980,7 +17034,15 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorino a vécu le soir, dans la chambre.
+narrateur|Il a joué avec la dînette.
+papa|Bravo, Victorino.
+papa|C'est du bon travail.
+maman|Bonne journée, mon grand.
+narrateur|La lampe reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16002,7 +17064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16040,6 +17102,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-021.xlsx
+++ b/stories/arbres/TREE-COL-021.xlsx
@@ -1197,17 +1197,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sous le portail, une flaque ronde tient le ciel. Le ciré jaune pend au crochet. Le capuchon lourd laisse une goutte. La goutte tombe près des bottes. Ça sent le cacao, près de la vitre. La vapeur dessine un nuage sur le verre. Papa pose deux tasses tièdes. Maman cherche un gant sur le radiateur. Un merle parle, derrière le portail. En ce moment, Victorino tire le ciré. Je veux la flaque ! Le ciel est dedans ! Papa parle du cacao, à maman. Les mots se cognent aux tasses. Tu disais, Victorino ? La flaque, le ciel ! Papa écoute maman, pas lui. Victorino ferme la bouche. Il attend, près du crochet. Le cacao fait un petit nuage. Voilà, je t'écoute. Je veux aller à la flaque. Avec quoi commençons-nous ?</t>
+          <t>Sous le portail, une flaque ronde tient le ciel. Le ciré jaune pend au crochet. Le capuchon lourd laisse une goutte. La goutte tombe près des bottes. Ça sent le cacao, près de la vitre. La vapeur dessine un nuage sur le verre. Papa pose deux tasses tièdes. Maman cherche un gant sur le radiateur. Un merle parle, derrière le portail. En ce moment, Victorino tire le ciré. Je veux la flaque ! Le ciel est dedans ! Papa parle du cacao, à maman. Les mots se cognent aux tasses. Tu disais, Victorino ? La flaque, le ciel ! Papa écoute maman, pas lui. Victorino ferme la bouche. Il attend, près du crochet. Le cacao fait un petit nuage. Voilà, je t'écoute. Je veux aller à la flaque. On commence avec quoi ?</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sous le portail, une flaque ronde tient le ciel. Le &lt;emphasis level="moderate"&gt;ciré jaune&lt;/emphasis&gt; pend au crochet. Le capuchon lourd laisse une goutte. La goutte tombe près des bottes. Ça sent le cacao, près de la vitre. La vapeur dessine un nuage sur le verre. Papa pose deux tasses tièdes. Maman cherche un gant sur le radiateur. Un merle parle, derrière le portail. En ce moment, Victorino tire le ciré. Je veux la flaque ! Le ciel est dedans ! Papa parle du cacao, à maman. Les mots se cognent aux tasses. Tu disais, Victorino ? La flaque, le ciel ! Papa écoute maman, pas lui. Victorino ferme la bouche. Il attend, près du crochet. Le cacao fait un petit nuage. Voilà, je t'écoute. Je veux aller à la flaque. Avec quoi commençons-nous ?&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sous le portail, une flaque ronde tient le ciel. Le &lt;emphasis level="moderate"&gt;ciré jaune&lt;/emphasis&gt; pend au crochet. Le capuchon lourd laisse une goutte. La goutte tombe près des bottes. Ça sent le cacao, près de la vitre. La vapeur dessine un nuage sur le verre. Papa pose deux tasses tièdes. Maman cherche un gant sur le radiateur. Un merle parle, derrière le portail. En ce moment, Victorino tire le ciré. Je veux la flaque ! Le ciel est dedans ! Papa parle du cacao, à maman. Les mots se cognent aux tasses. Tu disais, Victorino ? La flaque, le ciel ! Papa écoute maman, pas lui. Victorino ferme la bouche. Il attend, près du crochet. Le cacao fait un petit nuage. Voilà, je t'écoute. Je veux aller à la flaque. On commence avec quoi ?&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Sous le portail, une flaque ronde tient le ciel. Le &lt;emphasis&gt;ciré jaune&lt;/emphasis&gt; pend au crochet. Le capuchon lourd laisse une goutte. La goutte tombe près des bottes. Ça sent le cacao, près de la vitre. La vapeur dessine un nuage sur le verre. Papa pose deux tasses tièdes. Maman cherche un gant sur le radiateur. Un merle parle, derrière le portail. En ce moment, Victorino tire le ciré. Je veux la flaque ! Le ciel est dedans ! Papa parle du cacao, à maman. Les mots se cognent aux tasses. Tu disais, Victorino ? La flaque, le ciel ! Papa écoute maman, pas lui. Victorino ferme la bouche. Il attend, près du crochet. Le cacao fait un petit nuage. Voilà, je t'écoute. Je veux aller à la flaque. Avec quoi commençons-nous ? [pause]</t>
+          <t>Sous le portail, une flaque ronde tient le ciel. Le &lt;emphasis&gt;ciré jaune&lt;/emphasis&gt; pend au crochet. Le capuchon lourd laisse une goutte. La goutte tombe près des bottes. Ça sent le cacao, près de la vitre. La vapeur dessine un nuage sur le verre. Papa pose deux tasses tièdes. Maman cherche un gant sur le radiateur. Un merle parle, derrière le portail. En ce moment, Victorino tire le ciré. Je veux la flaque ! Le ciel est dedans ! Papa parle du cacao, à maman. Les mots se cognent aux tasses. Tu disais, Victorino ? La flaque, le ciel ! Papa écoute maman, pas lui. Victorino ferme la bouche. Il attend, près du crochet. Le cacao fait un petit nuage. Voilà, je t'écoute. Je veux aller à la flaque. On commence avec quoi ? [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1363,7 +1363,7 @@
 narrateur|Le cacao fait un petit nuage.
 papa|Voilà, je t'écoute.
 enfant-m|Je veux aller à la flaque.
-maman|Avec quoi commençons-nous ?</t>
+maman|On commence avec quoi ?</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1395,17 +1395,17 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Victorino peut prendre le ciré, les bottes, ou le bateau. Que prends-tu pour la flaque ?</t>
+          <t>Victorino peut prendre le ciré, les bottes, ou le bateau. Tu prends quoi, pour la flaque ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Victorino peut prendre le ciré, les bottes, ou le bateau. Que prends-tu pour la flaque ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Victorino peut prendre le ciré, les bottes, ou le bateau. Tu prends quoi, pour la flaque ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Victorino peut prendre le ciré, les bottes, ou le bateau. Que prends-tu pour la flaque ?&lt;/slow&gt; [long-pause]</t>
+          <t>&lt;slow&gt;Victorino peut prendre le ciré, les bottes, ou le bateau. Tu prends quoi, pour la flaque ?&lt;/slow&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
@@ -1564,7 +1564,7 @@
       <c r="AW3" t="inlineStr">
         <is>
           <t>narrateur|Victorino peut prendre le ciré, les bottes, ou le bateau.
-maman|Que prends-tu pour la flaque ?</t>
+maman|Tu prends quoi, pour la flaque ?</t>
         </is>
       </c>
     </row>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Quelque chose tombe du capuchon. Qu'est-ce qui tombe ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Quelque chose tombe du &lt;emphasis level="moderate"&gt;capuchon&lt;/emphasis&gt;. Qu'est-ce qui tombe ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>&lt;soft&gt;&lt;slow&gt;Quelque chose tombe du capuchon. Qu'est-ce qui tombe ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Quelque chose tombe du &lt;emphasis&gt;capuchon&lt;/emphasis&gt;. Qu'est-ce qui tombe ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>goutte</t>
+          <t>capuchon</t>
         </is>
       </c>
       <c r="AI5" s="2" t="n">
@@ -1977,12 +1977,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Une &lt;emphasis level="moderate"&gt;goutte&lt;/emphasis&gt; ! Oui, une goutte du capuchon. Cette fois, papa a entendu. Merci, Victorino. Nous t'avons entendu. Le ciré craque, un peu collant. Une feuille jaune colle à la poche. Ils avancent vers la porte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Une goutte ! Oui, une goutte du capuchon. Cette fois, papa a entendu. Merci, Victorino. Nous t'avons entendu. Le &lt;emphasis level="moderate"&gt;ciré&lt;/emphasis&gt; craque, un peu collant. Une feuille jaune colle à la poche. Ils avancent vers la porte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Une &lt;emphasis&gt;goutte&lt;/emphasis&gt; ! Oui, une goutte du capuchon. Cette fois, papa a entendu. Merci, Victorino. Nous t'avons entendu. Le ciré craque, un peu collant. Une feuille jaune colle à la poche. Ils avancent vers la porte. [pause]</t>
+          <t>Une goutte ! Oui, une goutte du capuchon. Cette fois, papa a entendu. Merci, Victorino. Nous t'avons entendu. Le &lt;emphasis&gt;ciré&lt;/emphasis&gt; craque, un peu collant. Une feuille jaune colle à la poche. Ils avancent vers la porte. [pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AH6" s="2" t="inlineStr">
         <is>
-          <t>goutte</t>
+          <t>ciré</t>
         </is>
       </c>
       <c r="AI6" s="2" t="n">
@@ -2150,17 +2150,17 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Dehors, l'eau brille en trois endroits. La flaque du portail, la gouttière, ou le bac ? Où allons-nous ?</t>
+          <t>Dehors, l'eau brille en trois endroits. La flaque du portail, la gouttière, ou le bac ? On va où ?</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Dehors, l'eau brille en trois endroits. La flaque du portail, la gouttière, ou le bac ? Où allons-nous ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Dehors, l'eau brille en trois endroits. La flaque du portail, la gouttière, ou le bac ? On va où ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Dehors, l'eau brille en trois endroits. La flaque du portail, la gouttière, ou le bac ? Où allons-nous ?&lt;/slow&gt; [long-pause]</t>
+          <t>&lt;slow&gt;Dehors, l'eau brille en trois endroits. La flaque du portail, la gouttière, ou le bac ? On va où ?&lt;/slow&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
@@ -2320,7 +2320,7 @@
         <is>
           <t>narrateur|Dehors, l'eau brille en trois endroits.
 papa|La flaque du portail, la gouttière, ou le bac ?
-maman|Où allons-nous ?</t>
+maman|On va où ?</t>
         </is>
       </c>
     </row>
@@ -6431,17 +6431,17 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Victorino choisit de regarder. Papa garde les mains loin de l'arrosoir. Il avance vers toi, Victorino. Victorino ne répond pas. Il laisse le silence au bateau. Maintenant, tu peux poser l'arrosoir. Papa attend que le papier touche l'herbe. Le ciré jaune sèche au soleil du bac.</t>
+          <t>Victorino choisit de regarder. Papa garde les mains loin de l'arrosoir. Une goutte reste au bec de l'arrosoir. Il avance vers toi, Victorino. Victorino ne répond pas. Il laisse le silence au bateau. Maintenant, tu peux poser l'arrosoir. Papa attend que le papier touche l'herbe. Le ciré jaune sèche au soleil du bac.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Victorino choisit de regarder. Papa garde les mains loin de l'arrosoir. Il avance vers toi, Victorino. Victorino ne répond pas. Il laisse le silence au bateau. Maintenant, tu peux poser l'arrosoir. Papa attend que le papier touche l'herbe. Le ciré jaune sèche au soleil du bac.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Victorino choisit de regarder. Papa garde les mains loin de l'arrosoir. Une &lt;emphasis level="moderate"&gt;goutte&lt;/emphasis&gt; reste au bec de l'arrosoir. Il avance vers toi, Victorino. Victorino ne répond pas. Il laisse le silence au bateau. Maintenant, tu peux poser l'arrosoir. Papa attend que le papier touche l'herbe. Le ciré jaune sèche au soleil du bac.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Victorino choisit de regarder. Papa garde les mains loin de l'arrosoir. Il avance vers toi, Victorino. Victorino ne répond pas. Il laisse le silence au bateau. Maintenant, tu peux poser l'arrosoir. Papa attend que le papier touche l'herbe. Le ciré jaune sèche au soleil du bac. [pause]</t>
+          <t>Victorino choisit de regarder. Papa garde les mains loin de l'arrosoir. Une &lt;emphasis&gt;goutte&lt;/emphasis&gt; reste au bec de l'arrosoir. Il avance vers toi, Victorino. Victorino ne répond pas. Il laisse le silence au bateau. Maintenant, tu peux poser l'arrosoir. Papa attend que le papier touche l'herbe. Le ciré jaune sèche au soleil du bac. [pause]</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -6577,6 +6577,7 @@
         <is>
           <t>narrateur|Victorino choisit de regarder.
 narrateur|Papa garde les mains loin de l'arrosoir.
+narrateur|Une goutte reste au bec de l'arrosoir.
 maman|Il avance vers toi, Victorino.
 narrateur|Victorino ne répond pas.
 narrateur|Il laisse le silence au bateau.
@@ -6796,17 +6797,17 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Victorino attrape les bottes vertes. Une botte est tiède, l'autre froide. Mes bottes, pour la flaque ! Maman cherche le gant, près du radiateur. Elle parle à papa du gant perdu. Les mots de Victorino tombent par terre. Maman ! Maman ne se tourne pas. Victorino pose une botte. Il attend, une chaussette à la main. Oui, je t'écoute. Il manque une chaussette. Elle chauffe, sur le radiateur. Maman tend la chaussette chaude. Victorino enfile le coton tiède. Les bottes font un petit ploc.</t>
+          <t>Victorino attrape les bottes vertes. Une botte est tiède, l'autre froide. Mes bottes, pour la flaque ! Maman cherche le gant, près du radiateur. Elle parle à papa du gant perdu. Les mots de Victorino tombent par terre. Maman ! Maman ne se tourne pas. Victorino pose une botte. Il attend, une chaussette à la main. Oui, je t'écoute. Il manque une chaussette. Elle chauffe, sur le radiateur. Maman tend la chaussette chaude. Victorino enfile le coton tiède. Elles font ploc.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Victorino attrape les &lt;emphasis level="moderate"&gt;bottes&lt;/emphasis&gt; vertes. Une botte est tiède, l'autre froide. Mes bottes, pour la flaque ! Maman cherche le gant, près du radiateur. Elle parle à papa du gant perdu. Les mots de Victorino tombent par terre. Maman ! Maman ne se tourne pas. Victorino pose une botte. Il attend, une chaussette à la main. Oui, je t'écoute. Il manque une chaussette. Elle chauffe, sur le radiateur. Maman tend la chaussette chaude. Victorino enfile le coton tiède. Les bottes font un petit ploc.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Victorino attrape les &lt;emphasis level="moderate"&gt;bottes&lt;/emphasis&gt; vertes. Une botte est tiède, l'autre froide. Mes bottes, pour la flaque ! Maman cherche le gant, près du radiateur. Elle parle à papa du gant perdu. Les mots de Victorino tombent par terre. Maman ! Maman ne se tourne pas. Victorino pose une botte. Il attend, une chaussette à la main. Oui, je t'écoute. Il manque une chaussette. Elle chauffe, sur le radiateur. Maman tend la chaussette chaude. Victorino enfile le coton tiède. Elles font ploc.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Victorino attrape les &lt;emphasis&gt;bottes&lt;/emphasis&gt; vertes. Une botte est tiède, l'autre froide. Mes bottes, pour la flaque ! Maman cherche le gant, près du radiateur. Elle parle à papa du gant perdu. Les mots de Victorino tombent par terre. Maman ! Maman ne se tourne pas. Victorino pose une botte. Il attend, une chaussette à la main. Oui, je t'écoute. Il manque une chaussette. Elle chauffe, sur le radiateur. Maman tend la chaussette chaude. Victorino enfile le coton tiède. Les bottes font un petit ploc. [pause]</t>
+          <t>Victorino attrape les &lt;emphasis&gt;bottes&lt;/emphasis&gt; vertes. Une botte est tiède, l'autre froide. Mes bottes, pour la flaque ! Maman cherche le gant, près du radiateur. Elle parle à papa du gant perdu. Les mots de Victorino tombent par terre. Maman ! Maman ne se tourne pas. Victorino pose une botte. Il attend, une chaussette à la main. Oui, je t'écoute. Il manque une chaussette. Elle chauffe, sur le radiateur. Maman tend la chaussette chaude. Victorino enfile le coton tiède. Elles font ploc. [pause]</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
@@ -6955,7 +6956,7 @@
 papa|Elle chauffe, sur le radiateur.
 narrateur|Maman tend la chaussette chaude.
 narrateur|Victorino enfile le coton tiède.
-papa|Les bottes font un petit ploc.</t>
+papa|Elles font ploc.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -6987,17 +6988,17 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Une botte attend son coton. Que manque-t-il, pour la botte ?</t>
+          <t>Une botte attend son coton. Il manque quoi, pour la botte ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Une botte attend son coton. Que manque-t-il, pour la botte ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Une &lt;emphasis level="moderate"&gt;botte&lt;/emphasis&gt; attend son coton. Il manque quoi, pour la botte ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>&lt;soft&gt;&lt;slow&gt;Une botte attend son coton. Que manque-t-il, pour la botte ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Une &lt;emphasis&gt;botte&lt;/emphasis&gt; attend son coton. Il manque quoi, pour la botte ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -7094,7 +7095,7 @@
       </c>
       <c r="AH33" s="2" t="inlineStr">
         <is>
-          <t>chaussette</t>
+          <t>botte</t>
         </is>
       </c>
       <c r="AI33" s="2" t="n">
@@ -7148,7 +7149,7 @@
       <c r="AW33" t="inlineStr">
         <is>
           <t>narrateur|Une botte attend son coton.
-maman|Que manque-t-il, pour la botte ?</t>
+maman|Il manque quoi, pour la botte ?</t>
         </is>
       </c>
     </row>
@@ -7175,17 +7176,17 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>La chaussette ! Oui, la chaussette du radiateur. Maman l'a entendue, cette fois. Merci, Victorino. Tes mots sont arrivés. Les bottes font un petit ploc. Une feuille colle à la botte. La porte s'ouvre un peu.</t>
+          <t>La chaussette ! Oui, la chaussette du radiateur. Maman a entendu, cette fois. Merci, Victorino. Tes mots sont arrivés. Les bottes font un petit ploc. Une feuille colle à la botte. La porte s'ouvre un peu.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;chaussette&lt;/emphasis&gt; ! Oui, la chaussette du radiateur. Maman l'a entendue, cette fois. Merci, Victorino. Tes mots sont arrivés. Les bottes font un petit ploc. Une feuille colle à la botte. La porte s'ouvre un peu.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La chaussette ! Oui, la chaussette du radiateur. Maman a entendu, cette fois. Merci, Victorino. Tes mots sont arrivés. Les &lt;emphasis level="moderate"&gt;bottes&lt;/emphasis&gt; font un petit ploc. Une feuille colle à la botte. La porte s'ouvre un peu.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>La &lt;emphasis&gt;chaussette&lt;/emphasis&gt; ! Oui, la chaussette du radiateur. Maman l'a entendue, cette fois. Merci, Victorino. Tes mots sont arrivés. Les bottes font un petit ploc. Une feuille colle à la botte. La porte s'ouvre un peu. [pause]</t>
+          <t>La chaussette ! Oui, la chaussette du radiateur. Maman a entendu, cette fois. Merci, Victorino. Tes mots sont arrivés. Les &lt;emphasis&gt;bottes&lt;/emphasis&gt; font un petit ploc. Une feuille colle à la botte. La porte s'ouvre un peu. [pause]</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
@@ -7266,7 +7267,7 @@
       </c>
       <c r="AH34" s="2" t="inlineStr">
         <is>
-          <t>chaussette</t>
+          <t>bottes</t>
         </is>
       </c>
       <c r="AI34" s="2" t="n">
@@ -7321,7 +7322,7 @@
         <is>
           <t>enfant-m|La chaussette !
 narrateur|Oui, la chaussette du radiateur.
-narrateur|Maman l'a entendue, cette fois.
+narrateur|Maman a entendu, cette fois.
 papa|Merci, Victorino.
 papa|Tes mots sont arrivés.
 narrateur|Les bottes font un petit ploc.
@@ -7353,17 +7354,17 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Dehors, l'eau brille en trois endroits. La flaque du portail, la gouttière, ou le bac ? Où allons-nous ?</t>
+          <t>Dehors, l'eau brille en trois endroits. La flaque du portail, la gouttière, ou le bac ? On va où ?</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Dehors, l'eau brille en trois endroits. La flaque du portail, la gouttière, ou le bac ? Où allons-nous ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Dehors, l'eau brille en trois endroits. La flaque du portail, la gouttière, ou le bac ? On va où ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Dehors, l'eau brille en trois endroits. La flaque du portail, la gouttière, ou le bac ? Où allons-nous ?&lt;/slow&gt; [long-pause]</t>
+          <t>&lt;slow&gt;Dehors, l'eau brille en trois endroits. La flaque du portail, la gouttière, ou le bac ? On va où ?&lt;/slow&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
@@ -7523,7 +7524,7 @@
         <is>
           <t>narrateur|Dehors, l'eau brille en trois endroits.
 papa|La flaque du portail, la gouttière, ou le bac ?
-maman|Où allons-nous ?</t>
+maman|On va où ?</t>
         </is>
       </c>
     </row>
@@ -11634,17 +11635,17 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Victorino choisit de regarder. Papa garde les mains loin de l'arrosoir. Il avance vers toi, Victorino. Victorino ne répond pas. Il laisse le silence au bateau. Maintenant, tu peux poser l'arrosoir. Papa attend que le papier touche l'herbe. Une botte reflète le bac calme.</t>
+          <t>Victorino choisit de regarder. Papa garde les mains loin de l'arrosoir. Une goutte reste au bec de l'arrosoir. Il avance vers toi, Victorino. Victorino ne répond pas. Il laisse le silence au bateau. Maintenant, tu peux poser l'arrosoir. Papa attend que le papier touche l'herbe. Une botte reflète le bac calme.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Victorino choisit de regarder. Papa garde les mains loin de l'arrosoir. Il avance vers toi, Victorino. Victorino ne répond pas. Il laisse le silence au bateau. Maintenant, tu peux poser l'arrosoir. Papa attend que le papier touche l'herbe. Une botte reflète le bac calme.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Victorino choisit de regarder. Papa garde les mains loin de l'arrosoir. Une &lt;emphasis level="moderate"&gt;goutte&lt;/emphasis&gt; reste au bec de l'arrosoir. Il avance vers toi, Victorino. Victorino ne répond pas. Il laisse le silence au bateau. Maintenant, tu peux poser l'arrosoir. Papa attend que le papier touche l'herbe. Une botte reflète le bac calme.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Victorino choisit de regarder. Papa garde les mains loin de l'arrosoir. Il avance vers toi, Victorino. Victorino ne répond pas. Il laisse le silence au bateau. Maintenant, tu peux poser l'arrosoir. Papa attend que le papier touche l'herbe. Une botte reflète le bac calme. [pause]</t>
+          <t>Victorino choisit de regarder. Papa garde les mains loin de l'arrosoir. Une &lt;emphasis&gt;goutte&lt;/emphasis&gt; reste au bec de l'arrosoir. Il avance vers toi, Victorino. Victorino ne répond pas. Il laisse le silence au bateau. Maintenant, tu peux poser l'arrosoir. Papa attend que le papier touche l'herbe. Une botte reflète le bac calme. [pause]</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
@@ -11780,6 +11781,7 @@
         <is>
           <t>narrateur|Victorino choisit de regarder.
 narrateur|Papa garde les mains loin de l'arrosoir.
+narrateur|Une goutte reste au bec de l'arrosoir.
 maman|Il avance vers toi, Victorino.
 narrateur|Victorino ne répond pas.
 narrateur|Il laisse le silence au bateau.
@@ -12190,17 +12192,17 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Victorino a un plan, pour l'eau. Que veut-il poser sur la flaque ?</t>
+          <t>Victorino a un plan, pour l'eau. Il veut poser quoi, sur la flaque ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Victorino a un plan, pour l'eau. Que veut-il poser sur la flaque ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Victorino a un plan, pour l'eau. Il veut poser quoi, sur la &lt;emphasis level="moderate"&gt;flaque&lt;/emphasis&gt; ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>&lt;soft&gt;&lt;slow&gt;Victorino a un plan, pour l'eau. Que veut-il poser sur la flaque ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Victorino a un plan, pour l'eau. Il veut poser quoi, sur la &lt;emphasis&gt;flaque&lt;/emphasis&gt; ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -12297,7 +12299,7 @@
       </c>
       <c r="AH61" s="2" t="inlineStr">
         <is>
-          <t>bateau</t>
+          <t>flaque</t>
         </is>
       </c>
       <c r="AI61" s="2" t="n">
@@ -12351,7 +12353,7 @@
       <c r="AW61" t="inlineStr">
         <is>
           <t>narrateur|Victorino a un plan, pour l'eau.
-papa|Que veut-il poser sur la flaque ?</t>
+papa|Il veut poser quoi, sur la flaque ?</t>
         </is>
       </c>
     </row>
@@ -12556,17 +12558,17 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Dehors, l'eau brille en trois endroits. La flaque du portail, la gouttière, ou le bac ? Où allons-nous ?</t>
+          <t>Dehors, l'eau brille en trois endroits. La flaque du portail, la gouttière, ou le bac ? On va où ?</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Dehors, l'eau brille en trois endroits. La flaque du portail, la gouttière, ou le bac ? Où allons-nous ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Dehors, l'eau brille en trois endroits. La flaque du portail, la gouttière, ou le bac ? On va où ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Dehors, l'eau brille en trois endroits. La flaque du portail, la gouttière, ou le bac ? Où allons-nous ?&lt;/slow&gt; [long-pause]</t>
+          <t>&lt;slow&gt;Dehors, l'eau brille en trois endroits. La flaque du portail, la gouttière, ou le bac ? On va où ?&lt;/slow&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
@@ -12726,7 +12728,7 @@
         <is>
           <t>narrateur|Dehors, l'eau brille en trois endroits.
 papa|La flaque du portail, la gouttière, ou le bac ?
-maman|Où allons-nous ?</t>
+maman|On va où ?</t>
         </is>
       </c>
     </row>
@@ -16837,17 +16839,17 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Victorino choisit de regarder. Papa garde les mains loin de l'arrosoir. Il avance vers toi, Victorino. Victorino ne répond pas. Il laisse le silence au bateau. Maintenant, tu peux poser l'arrosoir. Papa attend que le papier touche l'herbe. Le bateau sèche, plat comme une feuille.</t>
+          <t>Victorino choisit de regarder. Papa garde les mains loin de l'arrosoir. Une goutte reste au bec de l'arrosoir. Il avance vers toi, Victorino. Victorino ne répond pas. Il laisse le silence au bateau. Maintenant, tu peux poser l'arrosoir. Papa attend que le papier touche l'herbe. Le bateau sèche, plat comme une feuille.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Victorino choisit de regarder. Papa garde les mains loin de l'arrosoir. Il avance vers toi, Victorino. Victorino ne répond pas. Il laisse le silence au bateau. Maintenant, tu peux poser l'arrosoir. Papa attend que le papier touche l'herbe. Le bateau sèche, plat comme une feuille.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Victorino choisit de regarder. Papa garde les mains loin de l'arrosoir. Une &lt;emphasis level="moderate"&gt;goutte&lt;/emphasis&gt; reste au bec de l'arrosoir. Il avance vers toi, Victorino. Victorino ne répond pas. Il laisse le silence au bateau. Maintenant, tu peux poser l'arrosoir. Papa attend que le papier touche l'herbe. Le bateau sèche, plat comme une feuille.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Victorino choisit de regarder. Papa garde les mains loin de l'arrosoir. Il avance vers toi, Victorino. Victorino ne répond pas. Il laisse le silence au bateau. Maintenant, tu peux poser l'arrosoir. Papa attend que le papier touche l'herbe. Le bateau sèche, plat comme une feuille. [pause]</t>
+          <t>Victorino choisit de regarder. Papa garde les mains loin de l'arrosoir. Une &lt;emphasis&gt;goutte&lt;/emphasis&gt; reste au bec de l'arrosoir. Il avance vers toi, Victorino. Victorino ne répond pas. Il laisse le silence au bateau. Maintenant, tu peux poser l'arrosoir. Papa attend que le papier touche l'herbe. Le bateau sèche, plat comme une feuille. [pause]</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
@@ -16983,6 +16985,7 @@
         <is>
           <t>narrateur|Victorino choisit de regarder.
 narrateur|Papa garde les mains loin de l'arrosoir.
+narrateur|Une goutte reste au bec de l'arrosoir.
 maman|Il avance vers toi, Victorino.
 narrateur|Victorino ne répond pas.
 narrateur|Il laisse le silence au bateau.
@@ -17196,7 +17199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17253,6 +17256,13 @@
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
